--- a/src/main/resources/Preventivo.xlsx
+++ b/src/main/resources/Preventivo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30306"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danae\eclipse-workspace\CMOOffers\src\com\cmo\offers\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBD3965-7851-4889-8D3D-9857957EFADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{270A45A8-465D-4900-A0C0-0F94BB2D9609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MP" sheetId="8" r:id="rId1"/>
@@ -19,8 +19,11 @@
     <sheet name="SC2" sheetId="17" r:id="rId4"/>
     <sheet name="SC3" sheetId="18" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,570 +40,567 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="187">
+  <si>
+    <t>COPPER PRICE FORMULA</t>
+  </si>
+  <si>
+    <t>PERIOD</t>
+  </si>
+  <si>
+    <t>ALUMINIUM PRICE FORMULA</t>
+  </si>
+  <si>
+    <t>SILVER BASE PRICE</t>
+  </si>
+  <si>
+    <t>lme $/tonn</t>
+  </si>
+  <si>
+    <t>AVG AUG 2025</t>
+  </si>
+  <si>
+    <t>Ag    €/Kg</t>
+  </si>
+  <si>
+    <t>prime $/tonn</t>
+  </si>
+  <si>
+    <t>Copper financial (4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alluminium financial </t>
+  </si>
+  <si>
+    <t>Management  copper (6%)</t>
+  </si>
+  <si>
+    <t>Management  alluminium</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> change $/€</t>
+  </si>
+  <si>
+    <t>Cu    €/kg</t>
+  </si>
+  <si>
+    <t>Al    €/kg</t>
+  </si>
+  <si>
+    <t>CMO SpA - Via delle Orobie 159 - 24059 URGNANO (BG) - Italy</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Your request</t>
+  </si>
+  <si>
+    <t>Offer. Nr.</t>
+  </si>
+  <si>
+    <t>Offer Date</t>
+  </si>
+  <si>
+    <t>Rev.</t>
+  </si>
+  <si>
+    <t>GENERAL INFORMATION</t>
+  </si>
+  <si>
+    <t>RAW MATERIAL</t>
+  </si>
+  <si>
+    <t>MACHINING</t>
+  </si>
+  <si>
+    <t>SILVERING</t>
+  </si>
+  <si>
+    <t>ADDITIONAL OPERATIONS</t>
+  </si>
+  <si>
+    <t>PACk &amp; TRANSPORT</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>TOOLING</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>Rif</t>
+  </si>
+  <si>
+    <t>Document reference</t>
+  </si>
+  <si>
+    <t>Document Title</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>q.ty x year</t>
+  </si>
+  <si>
+    <t>Prod. Batch</t>
+  </si>
+  <si>
+    <t>Delivery Batch</t>
+  </si>
+  <si>
+    <t>Brut Weight Kg/pc.</t>
+  </si>
+  <si>
+    <t>Net Weight  Kg/pc.</t>
+  </si>
+  <si>
+    <t>Scrap Weight Kg/pc.</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Base Price €/Kg</t>
+  </si>
+  <si>
+    <t>Transf. Price €/Kg</t>
+  </si>
+  <si>
+    <t>Cost      €/pc.</t>
+  </si>
+  <si>
+    <t>Setup     €/pc.</t>
+  </si>
+  <si>
+    <t>Machining        €/pc.</t>
+  </si>
+  <si>
+    <t>Silver Weight g/pc.</t>
+  </si>
+  <si>
+    <t>Silver     Cost      €/pc.</t>
+  </si>
+  <si>
+    <t>Silvering Operation  €/pc.</t>
+  </si>
+  <si>
+    <t>Activity  €/pc.</t>
+  </si>
+  <si>
+    <t>packaging   €/pc.</t>
+  </si>
+  <si>
+    <t>transport €/pc</t>
+  </si>
+  <si>
+    <t>€/pc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PARTECIPATION COST</t>
+  </si>
+  <si>
+    <t>First date</t>
+  </si>
+  <si>
+    <t>Last date</t>
+  </si>
+  <si>
+    <t>DELIVERY TIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 70/80 working days minimum </t>
+  </si>
+  <si>
+    <t>DAP - EX WORKS</t>
+  </si>
+  <si>
+    <t>PAYMENT</t>
+  </si>
+  <si>
+    <t>usual</t>
+  </si>
+  <si>
+    <t>PACKAGING</t>
+  </si>
+  <si>
+    <t>carton box</t>
+  </si>
+  <si>
+    <t>PRICES</t>
+  </si>
+  <si>
+    <t>will be updated with the LME raw material price</t>
+  </si>
+  <si>
+    <t>VALIDITY</t>
+  </si>
+  <si>
+    <t>https://www.cmogroup.it/wp-content/uploads/2024/08/Condizioni-di-Fornitura-CMO-Rev.-Agosto-2024.pdf</t>
+  </si>
+  <si>
+    <t>OFFER</t>
+  </si>
+  <si>
+    <t>Nr.</t>
+  </si>
+  <si>
+    <t>01/25</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>Rev.:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Customer:</t>
+  </si>
+  <si>
+    <t>SCHNEIDER</t>
+  </si>
+  <si>
+    <t>Your request:</t>
+  </si>
+  <si>
+    <t>1234 / 25</t>
+  </si>
+  <si>
+    <t>Doc. reference:</t>
+  </si>
+  <si>
+    <t>AK00002433757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper bar </t>
+  </si>
+  <si>
+    <t>Drawing:</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Quantity x year:</t>
+  </si>
+  <si>
+    <t>Pr.Batch:</t>
+  </si>
+  <si>
+    <t>First delivery date:</t>
+  </si>
+  <si>
+    <t>Last delivery date:</t>
+  </si>
+  <si>
+    <t>Delivery Batch:</t>
+  </si>
+  <si>
+    <t>CDC</t>
+  </si>
+  <si>
+    <t>Tooling (Una tantum)</t>
+  </si>
+  <si>
+    <t>Q.ty</t>
+  </si>
+  <si>
+    <t>Cost (€)</t>
+  </si>
+  <si>
+    <t>Total (€)</t>
+  </si>
+  <si>
+    <t>% Ric</t>
+  </si>
+  <si>
+    <t>Price (€)</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>TOOL</t>
+  </si>
+  <si>
+    <t>Attrezzo di piega</t>
+  </si>
+  <si>
+    <t>Realizzazato internamente</t>
+  </si>
+  <si>
+    <t>Attrezzo lav mec</t>
+  </si>
+  <si>
+    <t>Beretta</t>
+  </si>
+  <si>
+    <t>Test di campionatura</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Total Cost (€)</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>Guaina</t>
+  </si>
+  <si>
+    <t>Rivetti</t>
+  </si>
+  <si>
+    <t>Dadi</t>
+  </si>
+  <si>
+    <t>bulloni e tap pad INOX</t>
+  </si>
+  <si>
+    <t>Raw material</t>
+  </si>
+  <si>
+    <t>Brut W. (Kg/pc)</t>
+  </si>
+  <si>
+    <t>Net W.  (Kg/pc)</t>
+  </si>
+  <si>
+    <t>Scrap W. (Kg/pc)</t>
+  </si>
+  <si>
+    <t>% Screp Value</t>
+  </si>
+  <si>
+    <t>Transf. Price (€/Kg)</t>
+  </si>
+  <si>
+    <t>Material Cost (€/pc)</t>
+  </si>
+  <si>
+    <t>LME ($/ton)</t>
+  </si>
+  <si>
+    <t>Change (€/$)</t>
+  </si>
+  <si>
+    <t>Material Cost (€/kg)</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>LAM. CU ETP 1000x2000x3 H065</t>
+  </si>
+  <si>
+    <t>Note mp</t>
+  </si>
+  <si>
+    <t>Fase</t>
+  </si>
+  <si>
+    <t>Machining &amp; Additional Operations</t>
+  </si>
+  <si>
+    <t>Int/Ext</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Cost       (€/ora - €/pz)</t>
+  </si>
+  <si>
+    <t>T. Setup (min)</t>
+  </si>
+  <si>
+    <t>T. Prod (sec)</t>
+  </si>
+  <si>
+    <t>Setup cost (€)</t>
+  </si>
+  <si>
+    <t>Prod. cost (€)</t>
+  </si>
+  <si>
+    <t>Setup Price</t>
+  </si>
+  <si>
+    <t>Prod Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progettazione </t>
+  </si>
+  <si>
+    <t>MACH</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>PRG</t>
+  </si>
+  <si>
+    <t>Taglio Laser</t>
+  </si>
+  <si>
+    <t>TL</t>
+  </si>
+  <si>
+    <t>Piega</t>
+  </si>
+  <si>
+    <t>PIE</t>
+  </si>
+  <si>
+    <t>Satinatura</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>Raggiatura Spigolo</t>
+  </si>
+  <si>
+    <t>LAV</t>
+  </si>
+  <si>
+    <t>Insulation</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>tinning 15µ</t>
+  </si>
+  <si>
+    <t>ADD</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>TIN</t>
+  </si>
+  <si>
+    <t>Controllo finale</t>
+  </si>
+  <si>
+    <t>Total Machining</t>
+  </si>
+  <si>
+    <t>Total Additional Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatments </t>
+  </si>
   <si>
     <t>Centro</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Oper. Cost (€/pc)</t>
+  </si>
+  <si>
+    <t>% Oper Ric</t>
+  </si>
+  <si>
+    <t>Oper. Price (€)</t>
+  </si>
+  <si>
+    <t>Q.ty Ag (gr)</t>
+  </si>
+  <si>
+    <t>Silver cost (€)</t>
+  </si>
+  <si>
+    <t>% Silver Ric</t>
+  </si>
+  <si>
+    <t>Silver Price (€)</t>
+  </si>
+  <si>
+    <t>Argentatura</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>Arg</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Unit Cost (€)</t>
+  </si>
+  <si>
+    <t>Total cost (€)</t>
+  </si>
+  <si>
+    <t>TRAS</t>
+  </si>
+  <si>
+    <t>Transport costs</t>
+  </si>
+  <si>
+    <t>PACK</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Materiali e Componenti</t>
   </si>
   <si>
     <t>Lavorazioni</t>
   </si>
   <si>
-    <t>Test di campionatura</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Materiali e Componenti</t>
-  </si>
-  <si>
-    <t>Piega</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>Attrezzo di piega</t>
-  </si>
-  <si>
-    <t>SCHNEIDER</t>
-  </si>
-  <si>
-    <t>AK00002433757</t>
-  </si>
-  <si>
-    <t>q.ty x year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copper bar </t>
-  </si>
-  <si>
-    <t>Attrezzo lav mec</t>
-  </si>
-  <si>
-    <t>COPPER PRICE FORMULA</t>
-  </si>
-  <si>
-    <t>lme $/tonn</t>
-  </si>
-  <si>
-    <t>AVG AUG 2025</t>
-  </si>
-  <si>
-    <t>prime $/tonn</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> change $/€</t>
-  </si>
-  <si>
-    <t>Cu    €/kg</t>
-  </si>
-  <si>
-    <t>ALUMINIUM PRICE FORMULA</t>
-  </si>
-  <si>
-    <t>Al    €/kg</t>
-  </si>
-  <si>
-    <t>SILVER BASE PRICE</t>
-  </si>
-  <si>
-    <t>Realizzazato internamente</t>
-  </si>
-  <si>
-    <t>Beretta</t>
-  </si>
-  <si>
-    <t>Drawing</t>
-  </si>
-  <si>
-    <t>Date:</t>
-  </si>
-  <si>
-    <t>Your request:</t>
-  </si>
-  <si>
-    <t>Doc. reference:</t>
-  </si>
-  <si>
-    <t>Customer:</t>
-  </si>
-  <si>
-    <t>Drawing:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description: </t>
-  </si>
-  <si>
-    <t>Rev.</t>
-  </si>
-  <si>
-    <t>Rev.:</t>
-  </si>
-  <si>
-    <t>Quantity x year:</t>
-  </si>
-  <si>
-    <t>Delivery Batch:</t>
-  </si>
-  <si>
-    <t>Pr.Batch:</t>
-  </si>
-  <si>
-    <t>Q.ty</t>
-  </si>
-  <si>
-    <t>First delivery date:</t>
-  </si>
-  <si>
-    <t>Last delivery date:</t>
-  </si>
-  <si>
-    <t>% Ric</t>
-  </si>
-  <si>
-    <t>Unit Cost (€)</t>
-  </si>
-  <si>
-    <t>Total Cost (€)</t>
-  </si>
-  <si>
-    <t>Cost (€)</t>
-  </si>
-  <si>
-    <t>Total (€)</t>
-  </si>
-  <si>
-    <t>Price (€)</t>
-  </si>
-  <si>
-    <t>01/25</t>
-  </si>
-  <si>
-    <t>Raw material</t>
-  </si>
-  <si>
-    <t>LAM. CU ETP 1000x2000x3 H065</t>
+    <t>AK0000584999</t>
+  </si>
+  <si>
+    <t>Copper bar model 2</t>
+  </si>
+  <si>
+    <t>A2</t>
   </si>
   <si>
     <t>Altro</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Brut Weight Kg/pc.</t>
-  </si>
-  <si>
-    <t>Net Weight  Kg/pc.</t>
-  </si>
-  <si>
-    <t>Scrap Weight Kg/pc.</t>
-  </si>
-  <si>
-    <t>Transf. Price €/Kg</t>
-  </si>
-  <si>
-    <t>CU</t>
+    <t>AK00005841111</t>
+  </si>
+  <si>
+    <t>Al bar model 3</t>
+  </si>
+  <si>
+    <t>A3</t>
   </si>
   <si>
     <t>AL</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>PERIOD</t>
-  </si>
-  <si>
-    <t>Ag    €/Kg</t>
-  </si>
-  <si>
-    <t>% Screp Value</t>
-  </si>
-  <si>
-    <t>Management  alluminium</t>
-  </si>
-  <si>
-    <t>Material Cost (€/kg)</t>
-  </si>
-  <si>
-    <t>Note mp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alluminium financial </t>
-  </si>
-  <si>
-    <t>Guaina</t>
-  </si>
-  <si>
-    <t>Rivetti</t>
-  </si>
-  <si>
-    <t>Dadi</t>
-  </si>
-  <si>
-    <t>bulloni e tap pad INOX</t>
-  </si>
-  <si>
-    <t>Copper financial (4%)</t>
-  </si>
-  <si>
-    <t>Management  copper (6%)</t>
-  </si>
-  <si>
-    <t>Tooling (Una tantum)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progettazione </t>
-  </si>
-  <si>
-    <t>Fase</t>
-  </si>
-  <si>
-    <t>Taglio Laser</t>
-  </si>
-  <si>
-    <t>T. Setup (min)</t>
-  </si>
-  <si>
-    <t>Satinatura</t>
-  </si>
-  <si>
-    <t>Raggiatura Spigolo</t>
-  </si>
-  <si>
-    <t>Controllo finale</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Argentatura</t>
-  </si>
-  <si>
-    <t>ARG</t>
-  </si>
-  <si>
-    <t>T. Prod (sec)</t>
-  </si>
-  <si>
-    <t>CMO SpA - Via delle Orobie 159 - 24059 URGNANO (BG) - Italy</t>
-  </si>
-  <si>
-    <t>RAW MATERIAL</t>
-  </si>
-  <si>
-    <t>MACHINING</t>
-  </si>
-  <si>
-    <t>SILVERING</t>
-  </si>
-  <si>
-    <t>ADDITIONAL OPERATIONS</t>
-  </si>
-  <si>
-    <t>Document reference</t>
-  </si>
-  <si>
-    <t>Document Title</t>
-  </si>
-  <si>
-    <t>Delivery Batch</t>
-  </si>
-  <si>
-    <t>Setup     €/pc.</t>
-  </si>
-  <si>
-    <t>Machining        €/pc.</t>
-  </si>
-  <si>
-    <t>Silver Weight g/pc.</t>
-  </si>
-  <si>
-    <t>Silver     Cost      €/pc.</t>
-  </si>
-  <si>
-    <t>Silvering Operation  €/pc.</t>
-  </si>
-  <si>
-    <t>Activity  €/pc.</t>
-  </si>
-  <si>
-    <t>packaging   €/pc.</t>
-  </si>
-  <si>
-    <t>€/pc.</t>
-  </si>
-  <si>
-    <t>DELIVERY TIME</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 70/80 working days minimum </t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DAP - EX WORKS</t>
-  </si>
-  <si>
-    <t>PAYMENT</t>
-  </si>
-  <si>
-    <t>usual</t>
-  </si>
-  <si>
-    <t>PACKAGING</t>
-  </si>
-  <si>
-    <t>carton box</t>
-  </si>
-  <si>
-    <t>PRICES</t>
-  </si>
-  <si>
-    <t>will be updated with the LME raw material price</t>
-  </si>
-  <si>
-    <t>VALIDITY</t>
-  </si>
-  <si>
-    <t>https://www.cmogroup.it/wp-content/uploads/2024/08/Condizioni-di-Fornitura-CMO-Rev.-Agosto-2024.pdf</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Q.ty Ag (gr)</t>
-  </si>
-  <si>
-    <t>Change (€/$)</t>
-  </si>
-  <si>
-    <t>LME ($/ton)</t>
-  </si>
-  <si>
-    <t>Transf. Price (€/Kg)</t>
-  </si>
-  <si>
-    <t>Scrap W. (Kg/pc)</t>
-  </si>
-  <si>
-    <t>Material Cost (€/pc)</t>
-  </si>
-  <si>
-    <t>Net W.  (Kg/pc)</t>
-  </si>
-  <si>
-    <t>Brut W. (Kg/pc)</t>
-  </si>
-  <si>
-    <t>Components</t>
-  </si>
-  <si>
-    <t>Cost       (€/ora - €/pz)</t>
-  </si>
-  <si>
-    <t>Total cost (€)</t>
-  </si>
-  <si>
-    <t>Int/Ext</t>
-  </si>
-  <si>
-    <t>1234 / 25</t>
-  </si>
-  <si>
-    <t>Insulation</t>
-  </si>
-  <si>
-    <t>tinning 15µ</t>
-  </si>
-  <si>
-    <t>Setup cost (€)</t>
-  </si>
-  <si>
-    <t>Prod. cost (€)</t>
-  </si>
-  <si>
-    <t>Oper. Cost (€/pc)</t>
-  </si>
-  <si>
-    <t>Oper. Price (€)</t>
-  </si>
-  <si>
-    <t>Silver cost (€)</t>
-  </si>
-  <si>
-    <t>Silver Price (€)</t>
-  </si>
-  <si>
-    <t>% Silver Ric</t>
-  </si>
-  <si>
-    <t>% Oper Ric</t>
-  </si>
-  <si>
-    <t>Packaging</t>
-  </si>
-  <si>
-    <t>Transport costs</t>
-  </si>
-  <si>
-    <t>Total Machining</t>
-  </si>
-  <si>
-    <t>ADD</t>
-  </si>
-  <si>
-    <t>MACH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatments </t>
-  </si>
-  <si>
-    <t>Machining &amp; Additional Operations</t>
-  </si>
-  <si>
-    <t>Total Additional Operations</t>
-  </si>
-  <si>
-    <t>Setup Price</t>
-  </si>
-  <si>
-    <t>Prod Price</t>
-  </si>
-  <si>
-    <t>PACK</t>
-  </si>
-  <si>
-    <t>CDC</t>
-  </si>
-  <si>
-    <t>TOOL</t>
-  </si>
-  <si>
-    <t>COMP</t>
-  </si>
-  <si>
-    <t>Nr.</t>
-  </si>
-  <si>
-    <t>TRAS</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>PRG</t>
-  </si>
-  <si>
-    <t>TL</t>
-  </si>
-  <si>
-    <t>PIE</t>
-  </si>
-  <si>
-    <t>SAT</t>
-  </si>
-  <si>
-    <t>LAV</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>TIN</t>
-  </si>
-  <si>
-    <t>Arg</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Your request</t>
-  </si>
-  <si>
-    <t>Offer. Nr.</t>
-  </si>
-  <si>
-    <t>Offer Date</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>transport €/pc</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PARTECIPATION COST</t>
-  </si>
-  <si>
-    <t>TOOLING</t>
-  </si>
-  <si>
-    <t>PACk &amp; TRANSPORT</t>
-  </si>
-  <si>
-    <t>First date</t>
-  </si>
-  <si>
-    <t>Last date</t>
-  </si>
-  <si>
-    <t>GENERAL INFORMATION</t>
-  </si>
-  <si>
-    <t>AK0000584999</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>Copper bar model 2</t>
-  </si>
-  <si>
-    <t>AK00005841111</t>
-  </si>
-  <si>
-    <t>Rif</t>
-  </si>
-  <si>
     <t>LAM. AL 1000x2000x3 H065</t>
-  </si>
-  <si>
-    <t>Al bar model 3</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Prod. Batch</t>
-  </si>
-  <si>
-    <t>Base Price €/Kg</t>
-  </si>
-  <si>
-    <t>Cost      €/pc.</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Center</t>
-  </si>
-  <si>
-    <t>OFFER</t>
   </si>
 </sst>
 </file>
@@ -2231,128 +2231,128 @@
     <xf numFmtId="4" fontId="13" fillId="7" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -2698,65 +2698,65 @@
   <dimension ref="B1:T16"/>
   <sheetFormatPr defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="7" width="7.109375" customWidth="1"/>
-    <col min="8" max="8" width="2.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="14" max="14" width="5.44140625" customWidth="1"/>
-    <col min="15" max="15" width="2.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" customWidth="1"/>
+    <col min="15" max="15" width="2.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="19.2" customHeight="1"/>
-    <row r="2" spans="2:20" s="1" customFormat="1" ht="38.4" customHeight="1">
+    <row r="1" spans="2:20" ht="19.149999999999999" customHeight="1"/>
+    <row r="2" spans="2:20" s="1" customFormat="1" ht="38.450000000000003" customHeight="1">
       <c r="B2" s="284" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C2" s="284"/>
       <c r="D2" s="286"/>
       <c r="E2" s="286"/>
       <c r="F2" s="284" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="G2" s="286"/>
       <c r="I2" s="284" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J2" s="284"/>
       <c r="K2" s="285"/>
       <c r="L2" s="285"/>
       <c r="M2" s="284" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="N2" s="286"/>
       <c r="P2" s="284" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="285"/>
       <c r="R2" s="285"/>
       <c r="S2" s="284" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="T2" s="286"/>
     </row>
-    <row r="3" spans="2:20" ht="25.2" customHeight="1">
+    <row r="3" spans="2:20" ht="25.15" customHeight="1">
       <c r="B3" s="5">
         <v>9645.7000000000007</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="290" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E3" s="291"/>
       <c r="F3" s="292" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G3" s="293"/>
       <c r="I3" s="5">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="290" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L3" s="291"/>
       <c r="M3" s="292" t="str">
@@ -2776,7 +2776,7 @@
         <v>1103.73</v>
       </c>
       <c r="Q3" s="287" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="R3" s="286"/>
       <c r="S3" s="288" t="str">
@@ -2785,13 +2785,13 @@
       </c>
       <c r="T3" s="289"/>
     </row>
-    <row r="4" spans="2:20" ht="25.2" customHeight="1">
+    <row r="4" spans="2:20" ht="25.15" customHeight="1">
       <c r="B4" s="6">
         <v>340</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="294" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E4" s="291"/>
       <c r="F4" s="292"/>
@@ -2801,13 +2801,13 @@
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="295" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L4" s="296"/>
       <c r="M4" s="292"/>
       <c r="N4" s="293"/>
     </row>
-    <row r="5" spans="2:20" ht="25.2" customHeight="1">
+    <row r="5" spans="2:20" ht="25.15" customHeight="1">
       <c r="B5" s="9">
         <f>((B3+B4)*(1+C5))</f>
         <v>10385.128000000001</v>
@@ -2816,7 +2816,7 @@
         <v>0.04</v>
       </c>
       <c r="D5" s="294" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E5" s="291"/>
       <c r="F5" s="292"/>
@@ -2829,13 +2829,13 @@
         <v>0</v>
       </c>
       <c r="K5" s="290" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="L5" s="291"/>
       <c r="M5" s="292"/>
       <c r="N5" s="293"/>
     </row>
-    <row r="6" spans="2:20" ht="25.2" customHeight="1">
+    <row r="6" spans="2:20" ht="25.15" customHeight="1">
       <c r="B6" s="9">
         <f>B5*(1+C6)</f>
         <v>11008.235680000002</v>
@@ -2844,7 +2844,7 @@
         <v>0.06</v>
       </c>
       <c r="D6" s="294" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E6" s="291"/>
       <c r="F6" s="292"/>
@@ -2857,19 +2857,19 @@
         <v>0</v>
       </c>
       <c r="K6" s="290" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="L6" s="291"/>
       <c r="M6" s="292"/>
       <c r="N6" s="293"/>
     </row>
-    <row r="7" spans="2:20" ht="25.2" customHeight="1">
+    <row r="7" spans="2:20" ht="25.15" customHeight="1">
       <c r="B7" s="7">
         <v>1.1631</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="294" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E7" s="291"/>
       <c r="F7" s="292"/>
@@ -2880,20 +2880,20 @@
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="294" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L7" s="291"/>
       <c r="M7" s="292"/>
       <c r="N7" s="293"/>
     </row>
-    <row r="8" spans="2:20" ht="25.2" customHeight="1">
+    <row r="8" spans="2:20" ht="25.15" customHeight="1">
       <c r="B8" s="10">
         <f>IF(OR(B7=0,B7=""),0,(B6/B7)/1000)</f>
         <v>9.4645651104806134</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="294" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8" s="291"/>
       <c r="F8" s="292"/>
@@ -2904,13 +2904,13 @@
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="294" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="L8" s="291"/>
       <c r="M8" s="292"/>
       <c r="N8" s="293"/>
     </row>
-    <row r="9" spans="2:20" ht="25.2" customHeight="1">
+    <row r="9" spans="2:20" ht="25.15" customHeight="1">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2918,19 +2918,19 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="2:20" ht="25.2" customHeight="1"/>
-    <row r="11" spans="2:20" ht="25.2" customHeight="1"/>
-    <row r="12" spans="2:20" ht="25.2" customHeight="1"/>
-    <row r="13" spans="2:20" ht="25.2" customHeight="1"/>
-    <row r="14" spans="2:20" ht="25.2" customHeight="1">
+    <row r="10" spans="2:20" ht="25.15" customHeight="1"/>
+    <row r="11" spans="2:20" ht="25.15" customHeight="1"/>
+    <row r="12" spans="2:20" ht="25.15" customHeight="1"/>
+    <row r="13" spans="2:20" ht="25.15" customHeight="1"/>
+    <row r="14" spans="2:20" ht="25.15" customHeight="1">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="2:20" ht="25.2" customHeight="1"/>
-    <row r="16" spans="2:20" ht="25.2" customHeight="1"/>
+    <row r="15" spans="2:20" ht="25.15" customHeight="1"/>
+    <row r="16" spans="2:20" ht="25.15" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="K5:L5"/>
@@ -2964,39 +2964,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5860D4-B900-4F8A-9AA7-58466905E106}">
   <dimension ref="A1:AE32"/>
-  <sheetFormatPr defaultColWidth="16.5546875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" style="14"/>
-    <col min="3" max="3" width="17.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="14"/>
+    <col min="3" max="3" width="17.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" style="14" customWidth="1"/>
     <col min="5" max="5" width="6" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" style="14" customWidth="1"/>
     <col min="7" max="7" width="8" style="14" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" style="14" customWidth="1"/>
-    <col min="15" max="15" width="11.109375" style="14" customWidth="1"/>
+    <col min="13" max="13" width="29.42578125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" style="14" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" style="14" customWidth="1"/>
     <col min="16" max="16" width="10" style="14" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" style="14" customWidth="1"/>
-    <col min="18" max="19" width="9.88671875" style="14" customWidth="1"/>
-    <col min="20" max="20" width="9.33203125" style="14" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" style="14" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.5546875" style="14" customWidth="1"/>
-    <col min="24" max="24" width="13.33203125" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.33203125" style="14" customWidth="1"/>
-    <col min="27" max="27" width="9.88671875" style="14" customWidth="1"/>
-    <col min="28" max="28" width="10.6640625" style="14" customWidth="1"/>
-    <col min="29" max="29" width="16.5546875" style="14"/>
+    <col min="17" max="17" width="9.28515625" style="14" customWidth="1"/>
+    <col min="18" max="19" width="9.85546875" style="14" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="14" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" style="14" customWidth="1"/>
+    <col min="24" max="24" width="15.85546875" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.140625" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" style="14" customWidth="1"/>
+    <col min="27" max="27" width="9.85546875" style="14" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" style="14" customWidth="1"/>
+    <col min="29" max="29" width="16.5703125" style="14"/>
     <col min="30" max="30" width="11" style="14" customWidth="1"/>
-    <col min="31" max="31" width="11.33203125" style="14" customWidth="1"/>
-    <col min="32" max="16384" width="16.5546875" style="14"/>
+    <col min="31" max="31" width="11.28515625" style="14" customWidth="1"/>
+    <col min="32" max="16384" width="16.5703125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -3035,7 +3035,7 @@
     <row r="2" spans="1:31">
       <c r="A2" s="168"/>
       <c r="B2" s="173" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D2" s="173"/>
       <c r="E2" s="174"/>
@@ -3099,15 +3099,12 @@
       <c r="AD3" s="172"/>
       <c r="AE3" s="168"/>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" ht="12.75">
       <c r="A4" s="168"/>
       <c r="B4" s="180" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="224" t="str">
-        <f>'SC1'!C2</f>
-        <v>SCHNEIDER</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C4" s="224"/>
       <c r="D4" s="181"/>
       <c r="E4" s="178"/>
       <c r="F4" s="170"/>
@@ -3137,15 +3134,12 @@
       <c r="AD4" s="172"/>
       <c r="AE4" s="168"/>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" ht="12.75">
       <c r="A5" s="168"/>
       <c r="B5" s="182" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="224" t="str">
-        <f>'SC1'!H2</f>
-        <v>1234 / 25</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C5" s="224"/>
       <c r="D5" s="181"/>
       <c r="E5" s="183"/>
       <c r="F5" s="170"/>
@@ -3175,15 +3169,12 @@
       <c r="AD5" s="172"/>
       <c r="AE5" s="168"/>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" ht="12.75">
       <c r="A6" s="168"/>
       <c r="B6" s="182" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="225" t="str">
-        <f>'SC1'!H1</f>
-        <v>01/25</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C6" s="225"/>
       <c r="D6" s="181"/>
       <c r="E6" s="184"/>
       <c r="F6" s="179"/>
@@ -3213,15 +3204,12 @@
       <c r="AD6" s="172"/>
       <c r="AE6" s="168"/>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" ht="12.75">
       <c r="A7" s="168"/>
       <c r="B7" s="182" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="226">
-        <f>'SC1'!J1</f>
-        <v>44599</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C7" s="226"/>
       <c r="D7" s="185"/>
       <c r="E7" s="184"/>
       <c r="F7" s="179"/>
@@ -3251,15 +3239,12 @@
       <c r="AD7" s="172"/>
       <c r="AE7" s="168"/>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" ht="12.75">
       <c r="A8" s="168"/>
       <c r="B8" s="182" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="227">
-        <f>'SC1'!L1</f>
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C8" s="227"/>
       <c r="D8" s="185"/>
       <c r="E8" s="184"/>
       <c r="F8" s="179"/>
@@ -3289,7 +3274,7 @@
       <c r="AD8" s="172"/>
       <c r="AE8" s="168"/>
     </row>
-    <row r="9" spans="1:31" ht="13.8" thickBot="1">
+    <row r="9" spans="1:31" ht="13.9" thickBot="1">
       <c r="A9" s="168"/>
       <c r="B9" s="181"/>
       <c r="C9" s="231"/>
@@ -3323,522 +3308,264 @@
       <c r="AE9" s="168"/>
     </row>
     <row r="10" spans="1:31" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A10" s="308" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="309"/>
-      <c r="C10" s="309"/>
-      <c r="D10" s="309"/>
-      <c r="E10" s="309"/>
-      <c r="F10" s="309"/>
-      <c r="G10" s="309"/>
-      <c r="H10" s="310"/>
-      <c r="I10" s="305" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="306"/>
-      <c r="K10" s="306"/>
-      <c r="L10" s="306"/>
-      <c r="M10" s="306"/>
-      <c r="N10" s="306"/>
-      <c r="O10" s="306"/>
-      <c r="P10" s="307"/>
-      <c r="Q10" s="305" t="s">
-        <v>85</v>
-      </c>
-      <c r="R10" s="307"/>
-      <c r="S10" s="306" t="s">
-        <v>86</v>
-      </c>
-      <c r="T10" s="306"/>
-      <c r="U10" s="307"/>
-      <c r="V10" s="305" t="s">
-        <v>87</v>
-      </c>
-      <c r="W10" s="306"/>
-      <c r="X10" s="306"/>
-      <c r="Y10" s="307"/>
-      <c r="Z10" s="305" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA10" s="306"/>
+      <c r="A10" s="281" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="282"/>
+      <c r="C10" s="282"/>
+      <c r="D10" s="282"/>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="283"/>
+      <c r="I10" s="278" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="279"/>
+      <c r="K10" s="279"/>
+      <c r="L10" s="279"/>
+      <c r="M10" s="279"/>
+      <c r="N10" s="279"/>
+      <c r="O10" s="279"/>
+      <c r="P10" s="280"/>
+      <c r="Q10" s="278" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="280"/>
+      <c r="S10" s="279" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" s="279"/>
+      <c r="U10" s="280"/>
+      <c r="V10" s="278" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" s="279"/>
+      <c r="X10" s="279"/>
+      <c r="Y10" s="280"/>
+      <c r="Z10" s="278" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA10" s="279"/>
       <c r="AB10" s="236" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="AC10" s="236" t="s">
-        <v>169</v>
-      </c>
-      <c r="AD10" s="305" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE10" s="307"/>
-    </row>
-    <row r="11" spans="1:31" ht="40.200000000000003" thickBot="1">
+        <v>28</v>
+      </c>
+      <c r="AD10" s="278" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE10" s="280"/>
+    </row>
+    <row r="11" spans="1:31" ht="37.5">
       <c r="A11" s="228" t="s">
-        <v>178</v>
+        <v>30</v>
       </c>
       <c r="B11" s="228" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="C11" s="228" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="D11" s="228" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E11" s="228" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F11" s="228" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G11" s="116" t="s">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="H11" s="116" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="I11" s="116" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="116" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="116" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="116" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="116" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="229" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="229" t="s">
+        <v>45</v>
+      </c>
+      <c r="R11" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="S11" s="116" t="s">
+        <v>47</v>
+      </c>
+      <c r="T11" s="116" t="s">
+        <v>48</v>
+      </c>
+      <c r="U11" s="116" t="s">
+        <v>49</v>
+      </c>
+      <c r="V11" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="W11" s="116" t="s">
+        <v>50</v>
+      </c>
+      <c r="X11" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y11" s="116" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z11" s="229" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="116" t="s">
+      <c r="AA11" s="229" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="116" t="s">
+      <c r="AB11" s="232" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="116" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" s="116" t="s">
-        <v>165</v>
-      </c>
-      <c r="N11" s="116" t="s">
-        <v>183</v>
-      </c>
-      <c r="O11" s="116" t="s">
+      <c r="AC11" s="232" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="229" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q11" s="229" t="s">
-        <v>91</v>
-      </c>
-      <c r="R11" s="116" t="s">
-        <v>92</v>
-      </c>
-      <c r="S11" s="116" t="s">
-        <v>93</v>
-      </c>
-      <c r="T11" s="116" t="s">
-        <v>94</v>
-      </c>
-      <c r="U11" s="116" t="s">
-        <v>95</v>
-      </c>
-      <c r="V11" s="116" t="s">
-        <v>57</v>
-      </c>
-      <c r="W11" s="116" t="s">
-        <v>96</v>
-      </c>
-      <c r="X11" s="116" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y11" s="116" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z11" s="229" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA11" s="229" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB11" s="232" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC11" s="232" t="s">
-        <v>168</v>
-      </c>
       <c r="AD11" s="229" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="AE11" s="230" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="14.4" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="14.45" customHeight="1">
       <c r="A12" s="249">
         <v>1</v>
       </c>
-      <c r="B12" s="237" t="str">
-        <f>'SC1'!$C$3</f>
-        <v>AK00002433757</v>
-      </c>
-      <c r="C12" s="237" t="str">
-        <f>'SC1'!$H$3</f>
-        <v xml:space="preserve">Copper bar </v>
-      </c>
-      <c r="D12" s="237" t="str">
-        <f>'SC1'!$C$4</f>
-        <v>AK00002433757</v>
-      </c>
-      <c r="E12" s="238" t="str">
-        <f>'SC1'!$G$4</f>
-        <v>A1</v>
-      </c>
-      <c r="F12" s="239">
-        <f>'SC1'!$J$4</f>
-        <v>14</v>
-      </c>
-      <c r="G12" s="239">
-        <f>'SC1'!$L$4</f>
-        <v>14</v>
-      </c>
-      <c r="H12" s="239">
-        <f>'SC1'!$J$5</f>
-        <v>14</v>
-      </c>
-      <c r="I12" s="240">
-        <f>'SC1'!$C$25</f>
-        <v>0.11</v>
-      </c>
-      <c r="J12" s="240">
-        <f>'SC1'!$D$25</f>
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="K12" s="240">
-        <f>I12-J12</f>
-        <v>2.4999999999999994E-2</v>
-      </c>
-      <c r="L12" s="241" t="str">
-        <f>'SC1'!A24</f>
-        <v>CU</v>
-      </c>
-      <c r="M12" s="238" t="str">
-        <f>'SC1'!$B$24</f>
-        <v>LAM. CU ETP 1000x2000x3 H065</v>
-      </c>
-      <c r="N12" s="242">
-        <f>'SC1'!$M$24</f>
-        <v>9.4645651104806134</v>
-      </c>
-      <c r="O12" s="243">
-        <f>'SC1'!$G$24</f>
-        <v>4.53</v>
-      </c>
-      <c r="P12" s="243">
-        <f>'SC1'!$J$25</f>
-        <v>1.3942729815149173</v>
-      </c>
-      <c r="Q12" s="243">
-        <f>'SC1'!$L$38</f>
-        <v>4.2142857142857144</v>
-      </c>
-      <c r="R12" s="243">
-        <f>'SC1'!$M$38</f>
-        <v>12.888888888888889</v>
-      </c>
-      <c r="S12" s="239">
-        <f>'SC1'!$J$42</f>
-        <v>10</v>
-      </c>
-      <c r="T12" s="244">
-        <f>'SC1'!$M$42</f>
-        <v>12.141030000000001</v>
-      </c>
-      <c r="U12" s="243">
-        <f>'SC1'!$I$42</f>
-        <v>3.9000000000000004</v>
-      </c>
-      <c r="V12" s="245" t="s">
-        <v>164</v>
-      </c>
-      <c r="W12" s="243">
-        <f>'SC1'!$M$39</f>
-        <v>1.32</v>
-      </c>
-      <c r="X12" s="240" t="str">
-        <f>'SC1'!B15</f>
-        <v>Components</v>
-      </c>
-      <c r="Y12" s="243">
-        <f>'SC1'!$G$21</f>
-        <v>10.6</v>
-      </c>
-      <c r="Z12" s="243">
-        <f>'SC1'!$E$47</f>
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="AA12" s="243">
-        <f>'SC1'!$E$46</f>
-        <v>5.9499999999999997E-2</v>
-      </c>
+      <c r="B12" s="237"/>
+      <c r="C12" s="237"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="238"/>
+      <c r="F12" s="239"/>
+      <c r="G12" s="239"/>
+      <c r="H12" s="239"/>
+      <c r="I12" s="240"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="240"/>
+      <c r="L12" s="241"/>
+      <c r="M12" s="238"/>
+      <c r="N12" s="242"/>
+      <c r="O12" s="243"/>
+      <c r="P12" s="243"/>
+      <c r="Q12" s="243"/>
+      <c r="R12" s="243"/>
+      <c r="S12" s="239"/>
+      <c r="T12" s="244"/>
+      <c r="U12" s="243"/>
+      <c r="V12" s="245"/>
+      <c r="W12" s="243"/>
+      <c r="X12" s="240"/>
+      <c r="Y12" s="243"/>
+      <c r="Z12" s="243"/>
+      <c r="AA12" s="243"/>
       <c r="AB12" s="246">
         <f>SUM(P12:R12)+SUM(T12:U12)+W12+Y12+Z12+AA12</f>
-        <v>46.560477584689515</v>
-      </c>
-      <c r="AC12" s="247">
-        <f>'SC1'!$G$13</f>
-        <v>3025</v>
-      </c>
-      <c r="AD12" s="248">
-        <f>'SC1'!C5</f>
-        <v>45803</v>
-      </c>
-      <c r="AE12" s="248">
-        <f>'SC1'!G5</f>
-        <v>45950</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="14.4" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="247"/>
+      <c r="AD12" s="248"/>
+      <c r="AE12" s="248"/>
+    </row>
+    <row r="13" spans="1:31" ht="14.45" customHeight="1">
       <c r="A13" s="249">
         <v>2</v>
       </c>
-      <c r="B13" s="186" t="str">
-        <f>'SC2'!$C$3</f>
-        <v>AK0000584999</v>
-      </c>
-      <c r="C13" s="186" t="str">
-        <f>'SC2'!$H$3</f>
-        <v>Copper bar model 2</v>
-      </c>
-      <c r="D13" s="186" t="str">
-        <f>'SC2'!$C$4</f>
-        <v>AK0000584999</v>
-      </c>
-      <c r="E13" s="93" t="str">
-        <f>'SC2'!$G$4</f>
-        <v>A2</v>
-      </c>
-      <c r="F13" s="187">
-        <f>'SC2'!$J$4</f>
-        <v>15</v>
-      </c>
-      <c r="G13" s="187">
-        <f>'SC2'!$L$4</f>
-        <v>15</v>
-      </c>
-      <c r="H13" s="187">
-        <f>'SC2'!$J$5</f>
-        <v>15</v>
-      </c>
-      <c r="I13" s="188">
-        <f>'SC2'!$C$25</f>
-        <v>0.22</v>
-      </c>
-      <c r="J13" s="188">
-        <f>'SC2'!$D$25</f>
-        <v>0.1</v>
-      </c>
-      <c r="K13" s="188">
-        <f>I13-J13</f>
-        <v>0.12</v>
-      </c>
-      <c r="L13" s="189" t="str">
-        <f>'SC2'!$A$24</f>
-        <v>CU</v>
-      </c>
-      <c r="M13" s="93" t="str">
-        <f>'SC2'!$B$24</f>
-        <v>LAM. CU ETP 1000x2000x3 H065</v>
-      </c>
-      <c r="N13" s="190">
-        <f>'SC2'!$M$24</f>
-        <v>9.4645651104806134</v>
-      </c>
-      <c r="O13" s="191">
-        <f>'SC2'!$G$24</f>
-        <v>4.53</v>
-      </c>
-      <c r="P13" s="191">
-        <f>'SC2'!$J$25</f>
-        <v>2.3821842572435736</v>
-      </c>
-      <c r="Q13" s="191">
-        <f>'SC2'!$L$38</f>
-        <v>6.2666666666666675</v>
-      </c>
-      <c r="R13" s="191">
-        <f>'SC2'!$M$38</f>
-        <v>12.888888888888889</v>
-      </c>
-      <c r="S13" s="187">
-        <f>'SC2'!$J$42</f>
-        <v>10</v>
-      </c>
-      <c r="T13" s="192">
-        <f>'SC2'!$M$42</f>
-        <v>12.141030000000001</v>
-      </c>
-      <c r="U13" s="191">
-        <f>'SC2'!$I$42</f>
-        <v>5.2</v>
-      </c>
-      <c r="V13" s="193" t="s">
-        <v>164</v>
-      </c>
-      <c r="W13" s="191">
-        <f>'SC2'!$M$39</f>
-        <v>1.32</v>
-      </c>
-      <c r="X13" s="188" t="str">
-        <f>'SC1'!B16</f>
-        <v>Guaina</v>
-      </c>
-      <c r="Y13" s="191">
-        <f>'SC2'!$G$21</f>
-        <v>21.2</v>
-      </c>
-      <c r="Z13" s="191">
-        <f>'SC2'!$E$47</f>
-        <v>0.05</v>
-      </c>
-      <c r="AA13" s="191">
-        <f>'SC2'!$E$46</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
+      <c r="B13" s="186"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="187"/>
+      <c r="G13" s="187"/>
+      <c r="H13" s="187"/>
+      <c r="I13" s="188"/>
+      <c r="J13" s="188"/>
+      <c r="K13" s="188"/>
+      <c r="L13" s="189"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="190"/>
+      <c r="O13" s="191"/>
+      <c r="P13" s="191"/>
+      <c r="Q13" s="191"/>
+      <c r="R13" s="191"/>
+      <c r="S13" s="187"/>
+      <c r="T13" s="192"/>
+      <c r="U13" s="191"/>
+      <c r="V13" s="193"/>
+      <c r="W13" s="191"/>
+      <c r="X13" s="188"/>
+      <c r="Y13" s="191"/>
+      <c r="Z13" s="191"/>
+      <c r="AA13" s="191"/>
       <c r="AB13" s="233">
         <f>SUM(P13:R13)+SUM(T13:U13)+W13+Y13+Z13+AA13</f>
-        <v>61.518769812799128</v>
-      </c>
-      <c r="AC13" s="194">
-        <f>'SC2'!$G$13</f>
-        <v>4730</v>
-      </c>
-      <c r="AD13" s="195">
-        <f>'SC2'!$C$5</f>
-        <v>45803</v>
-      </c>
-      <c r="AE13" s="195">
-        <f>'SC1'!$G$5</f>
-        <v>45950</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="194"/>
+      <c r="AD13" s="195"/>
+      <c r="AE13" s="195"/>
+    </row>
+    <row r="14" spans="1:31" ht="12.75">
       <c r="A14" s="249">
         <v>3</v>
       </c>
-      <c r="B14" s="186" t="str">
-        <f>'SC3'!$C$3</f>
-        <v>AK00005841111</v>
-      </c>
-      <c r="C14" s="186" t="str">
-        <f>'SC3'!$H$3</f>
-        <v>Al bar model 3</v>
-      </c>
-      <c r="D14" s="186" t="str">
-        <f>'SC3'!$C$4</f>
-        <v>AK00005841111</v>
-      </c>
-      <c r="E14" s="93" t="str">
-        <f>'SC3'!$G$4</f>
-        <v>A3</v>
-      </c>
-      <c r="F14" s="187">
-        <f>'SC3'!$J$4</f>
-        <v>16</v>
-      </c>
-      <c r="G14" s="187">
-        <f>'SC3'!$L$4</f>
-        <v>16</v>
-      </c>
-      <c r="H14" s="187">
-        <f>'SC3'!$J$5</f>
-        <v>16</v>
-      </c>
-      <c r="I14" s="188">
-        <f>'SC3'!$C$25</f>
-        <v>2</v>
-      </c>
-      <c r="J14" s="188">
-        <f>'SC3'!$D$25</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="188">
-        <f>I14-J14</f>
-        <v>1</v>
-      </c>
-      <c r="L14" s="189" t="str">
-        <f>'SC3'!$A$24</f>
-        <v>AL</v>
-      </c>
-      <c r="M14" s="93" t="str">
-        <f>'SC3'!$B$24</f>
-        <v>LAM. AL 1000x2000x3 H065</v>
-      </c>
-      <c r="N14" s="190">
-        <f>'SC3'!$M$24</f>
-        <v>2.2300748001031723</v>
-      </c>
-      <c r="O14" s="191">
-        <f>'SC3'!$G$24</f>
-        <v>4.53</v>
-      </c>
-      <c r="P14" s="191">
-        <f>'SC3'!$J$25</f>
-        <v>11.959097240134124</v>
-      </c>
-      <c r="Q14" s="191">
-        <f>'SC3'!$L$38</f>
-        <v>10.25</v>
-      </c>
-      <c r="R14" s="191">
-        <f>'SC3'!$M$38</f>
-        <v>12.888888888888889</v>
-      </c>
-      <c r="S14" s="187">
-        <f>'SC3'!$J$42</f>
-        <v>20</v>
-      </c>
-      <c r="T14" s="192">
-        <f>'SC3'!$M$42</f>
-        <v>24.282060000000001</v>
-      </c>
-      <c r="U14" s="191">
-        <f>'SC3'!$I$42</f>
-        <v>5.2</v>
-      </c>
-      <c r="V14" s="193" t="s">
-        <v>164</v>
-      </c>
-      <c r="W14" s="191">
-        <f>'SC3'!$M$39</f>
-        <v>1.32</v>
-      </c>
-      <c r="X14" s="188" t="str">
-        <f>'SC1'!B17</f>
-        <v>Rivetti</v>
-      </c>
-      <c r="Y14" s="191">
-        <f>'SC3'!$G$21</f>
-        <v>31.8</v>
-      </c>
-      <c r="Z14" s="191">
-        <f>'SC3'!$E$47</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA14" s="191">
-        <f>'SC3'!$E$46</f>
-        <v>0.7</v>
-      </c>
+      <c r="B14" s="186"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="186"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="187"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="188"/>
+      <c r="J14" s="188"/>
+      <c r="K14" s="188"/>
+      <c r="L14" s="189"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="190"/>
+      <c r="O14" s="191"/>
+      <c r="P14" s="191"/>
+      <c r="Q14" s="191"/>
+      <c r="R14" s="191"/>
+      <c r="S14" s="187"/>
+      <c r="T14" s="192"/>
+      <c r="U14" s="191"/>
+      <c r="V14" s="193"/>
+      <c r="W14" s="191"/>
+      <c r="X14" s="188"/>
+      <c r="Y14" s="191"/>
+      <c r="Z14" s="191"/>
+      <c r="AA14" s="191"/>
       <c r="AB14" s="233">
         <f>SUM(P14:R14)+SUM(T14:U14)+W14+Y14+Z14+AA14</f>
-        <v>98.900046129023011</v>
-      </c>
-      <c r="AC14" s="194">
-        <f>'SC3'!$G$13</f>
-        <v>7095</v>
-      </c>
-      <c r="AD14" s="195">
-        <f>'SC3'!$C$5</f>
-        <v>45803</v>
-      </c>
-      <c r="AE14" s="195">
-        <f>'SC3'!$G$5</f>
-        <v>45950</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="194"/>
+      <c r="AD14" s="195"/>
+      <c r="AE14" s="195"/>
     </row>
     <row r="15" spans="1:31">
       <c r="A15" s="249">
@@ -4121,16 +3848,16 @@
     <row r="23" spans="1:31">
       <c r="A23" s="168"/>
       <c r="B23" s="219" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="301" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="302"/>
-      <c r="E23" s="302"/>
-      <c r="F23" s="302"/>
-      <c r="G23" s="302"/>
-      <c r="H23" s="303"/>
+        <v>57</v>
+      </c>
+      <c r="C23" s="274" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="275"/>
+      <c r="E23" s="275"/>
+      <c r="F23" s="275"/>
+      <c r="G23" s="275"/>
+      <c r="H23" s="276"/>
       <c r="I23" s="172"/>
       <c r="J23" s="168"/>
       <c r="K23" s="220"/>
@@ -4158,16 +3885,16 @@
     <row r="24" spans="1:31">
       <c r="A24" s="168"/>
       <c r="B24" s="221" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="301" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="302"/>
-      <c r="E24" s="302"/>
-      <c r="F24" s="302"/>
-      <c r="G24" s="302"/>
-      <c r="H24" s="303"/>
+        <v>29</v>
+      </c>
+      <c r="C24" s="274" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="275"/>
+      <c r="E24" s="275"/>
+      <c r="F24" s="275"/>
+      <c r="G24" s="275"/>
+      <c r="H24" s="276"/>
       <c r="I24" s="172"/>
       <c r="J24" s="168"/>
       <c r="K24" s="220"/>
@@ -4195,16 +3922,16 @@
     <row r="25" spans="1:31">
       <c r="A25" s="168"/>
       <c r="B25" s="219" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="301" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="302"/>
-      <c r="E25" s="302"/>
-      <c r="F25" s="302"/>
-      <c r="G25" s="302"/>
-      <c r="H25" s="303"/>
+        <v>60</v>
+      </c>
+      <c r="C25" s="274" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="275"/>
+      <c r="E25" s="275"/>
+      <c r="F25" s="275"/>
+      <c r="G25" s="275"/>
+      <c r="H25" s="276"/>
       <c r="I25" s="172"/>
       <c r="J25" s="168"/>
       <c r="K25" s="220"/>
@@ -4232,16 +3959,16 @@
     <row r="26" spans="1:31">
       <c r="A26" s="168"/>
       <c r="B26" s="219" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="301" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="302"/>
-      <c r="E26" s="302"/>
-      <c r="F26" s="302"/>
-      <c r="G26" s="302"/>
-      <c r="H26" s="303"/>
+        <v>62</v>
+      </c>
+      <c r="C26" s="274" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="275"/>
+      <c r="E26" s="275"/>
+      <c r="F26" s="275"/>
+      <c r="G26" s="275"/>
+      <c r="H26" s="276"/>
       <c r="I26" s="172"/>
       <c r="J26" s="168"/>
       <c r="K26" s="220"/>
@@ -4269,16 +3996,16 @@
     <row r="27" spans="1:31">
       <c r="A27" s="168"/>
       <c r="B27" s="219" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="304" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="304"/>
-      <c r="E27" s="304"/>
-      <c r="F27" s="304"/>
-      <c r="G27" s="304"/>
-      <c r="H27" s="304"/>
+        <v>64</v>
+      </c>
+      <c r="C27" s="277" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="277"/>
+      <c r="E27" s="277"/>
+      <c r="F27" s="277"/>
+      <c r="G27" s="277"/>
+      <c r="H27" s="277"/>
       <c r="I27" s="172"/>
       <c r="J27" s="168"/>
       <c r="K27" s="220"/>
@@ -4306,14 +4033,14 @@
     <row r="28" spans="1:31">
       <c r="A28" s="168"/>
       <c r="B28" s="222" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="297"/>
-      <c r="D28" s="298"/>
-      <c r="E28" s="298"/>
-      <c r="F28" s="298"/>
-      <c r="G28" s="298"/>
-      <c r="H28" s="299"/>
+        <v>66</v>
+      </c>
+      <c r="C28" s="270"/>
+      <c r="D28" s="271"/>
+      <c r="E28" s="271"/>
+      <c r="F28" s="271"/>
+      <c r="G28" s="271"/>
+      <c r="H28" s="272"/>
       <c r="I28" s="172"/>
       <c r="J28" s="168"/>
       <c r="K28" s="220"/>
@@ -4340,15 +4067,15 @@
     </row>
     <row r="29" spans="1:31">
       <c r="A29" s="168"/>
-      <c r="B29" s="300" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="300"/>
-      <c r="D29" s="300"/>
-      <c r="E29" s="300"/>
-      <c r="F29" s="300"/>
-      <c r="G29" s="300"/>
-      <c r="H29" s="300"/>
+      <c r="B29" s="273" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="273"/>
+      <c r="D29" s="273"/>
+      <c r="E29" s="273"/>
+      <c r="F29" s="273"/>
+      <c r="G29" s="273"/>
+      <c r="H29" s="273"/>
       <c r="I29" s="172"/>
       <c r="J29" s="168"/>
       <c r="K29" s="220"/>
@@ -4510,146 +4237,146 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" style="14" customWidth="1"/>
-    <col min="3" max="5" width="11.6640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="14" customWidth="1"/>
-    <col min="8" max="9" width="10.6640625" style="14" customWidth="1"/>
-    <col min="10" max="11" width="11.33203125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="82.6640625" style="13" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="14"/>
+    <col min="1" max="1" width="5.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" style="14" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="14" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="14" customWidth="1"/>
+    <col min="10" max="11" width="11.28515625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="82.7109375" style="13" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.8" thickBot="1">
+    <row r="1" spans="1:14" ht="13.9" thickBot="1">
       <c r="B1" s="36" t="s">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="12"/>
       <c r="G1" s="37" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="J1" s="48">
         <v>44599</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L1" s="49">
         <v>0</v>
       </c>
       <c r="M1" s="50"/>
       <c r="N1" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20.399999999999999" customHeight="1" thickBot="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20.45" customHeight="1" thickBot="1">
       <c r="B2" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="274" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="275"/>
-      <c r="E2" s="276"/>
+        <v>74</v>
+      </c>
+      <c r="C2" s="297" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="298"/>
+      <c r="E2" s="299"/>
       <c r="F2" s="38" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="274" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="277"/>
+      <c r="H2" s="297" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="298"/>
+      <c r="J2" s="298"/>
+      <c r="K2" s="298"/>
+      <c r="L2" s="305"/>
       <c r="M2" s="34"/>
       <c r="N2" s="13" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" thickBot="1">
       <c r="B3" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="278" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="279"/>
-      <c r="E3" s="280"/>
+        <v>78</v>
+      </c>
+      <c r="C3" s="300" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="301"/>
+      <c r="E3" s="302"/>
       <c r="F3" s="39" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G3" s="16"/>
-      <c r="H3" s="281" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="282"/>
-      <c r="J3" s="282"/>
-      <c r="K3" s="282"/>
-      <c r="L3" s="283"/>
+      <c r="H3" s="306" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="307"/>
+      <c r="J3" s="307"/>
+      <c r="K3" s="307"/>
+      <c r="L3" s="308"/>
       <c r="M3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" thickBot="1">
       <c r="B4" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="278" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="279"/>
-      <c r="E4" s="280"/>
+        <v>82</v>
+      </c>
+      <c r="C4" s="300" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="301"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="39" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="52">
         <v>14</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="L4" s="53">
         <v>14</v>
       </c>
       <c r="M4" s="54"/>
     </row>
-    <row r="5" spans="1:14" ht="13.8" thickBot="1">
+    <row r="5" spans="1:14" ht="13.9" thickBot="1">
       <c r="B5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="272">
+        <v>86</v>
+      </c>
+      <c r="C5" s="303">
         <v>45803</v>
       </c>
-      <c r="D5" s="273"/>
+      <c r="D5" s="304"/>
       <c r="E5" s="166" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133">
         <v>45950</v>
       </c>
       <c r="H5" s="166" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="I5" s="134"/>
       <c r="J5" s="135">
@@ -4660,7 +4387,7 @@
       <c r="M5" s="54"/>
       <c r="N5" s="41"/>
     </row>
-    <row r="6" spans="1:14" ht="13.8" thickBot="1">
+    <row r="6" spans="1:14" ht="13.9" thickBot="1">
       <c r="B6" s="268"/>
       <c r="C6" s="266"/>
       <c r="D6" s="266"/>
@@ -4677,25 +4404,25 @@
     </row>
     <row r="7" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A7" s="269" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C7" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D7" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E7" s="117" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F7" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G7" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="17"/>
@@ -4704,15 +4431,15 @@
       <c r="L7" s="18"/>
       <c r="M7" s="55"/>
       <c r="N7" s="261" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="42" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C8" s="56">
         <v>1</v>
@@ -4737,15 +4464,15 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="13" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C9" s="60">
         <v>2</v>
@@ -4770,15 +4497,15 @@
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="13" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C10" s="60">
         <v>1</v>
@@ -4805,7 +4532,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="60"/>
@@ -4827,9 +4554,9 @@
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
     </row>
-    <row r="12" spans="1:14" ht="13.8" thickBot="1">
+    <row r="12" spans="1:14" ht="13.9" thickBot="1">
       <c r="A12" s="44" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="64"/>
@@ -4854,10 +4581,10 @@
     <row r="13" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="138"/>
       <c r="B13" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C13" s="139" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="D13" s="139"/>
       <c r="E13" s="140">
@@ -4876,7 +4603,7 @@
       <c r="M13" s="24"/>
       <c r="N13" s="25"/>
     </row>
-    <row r="14" spans="1:14" ht="13.8" thickBot="1">
+    <row r="14" spans="1:14" ht="13.9" thickBot="1">
       <c r="A14" s="262"/>
       <c r="B14" s="262"/>
       <c r="C14" s="262"/>
@@ -4894,33 +4621,33 @@
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A15" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B15" s="251" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D15" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E15" s="117" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F15" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G15" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C16" s="68">
         <v>1</v>
@@ -4942,10 +4669,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C17" s="73">
         <v>1</v>
@@ -4967,10 +4694,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C18" s="73">
         <v>1</v>
@@ -4992,10 +4719,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C19" s="73">
         <v>1</v>
@@ -5015,9 +4742,9 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.8" thickBot="1">
+    <row r="20" spans="1:14" ht="13.9" thickBot="1">
       <c r="A20" s="45" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="77"/>
@@ -5037,7 +4764,7 @@
     <row r="21" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="138"/>
       <c r="B21" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21" s="139"/>
       <c r="D21" s="139"/>
@@ -5058,7 +4785,7 @@
       <c r="M21" s="24"/>
       <c r="N21" s="25"/>
     </row>
-    <row r="22" spans="1:14" ht="13.8" thickBot="1">
+    <row r="22" spans="1:14" ht="13.9" thickBot="1">
       <c r="B22" s="131"/>
       <c r="C22" s="125"/>
       <c r="D22" s="126"/>
@@ -5075,52 +4802,52 @@
     </row>
     <row r="23" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A23" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B23" s="251" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="C23" s="117" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D23" s="117" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E23" s="117" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="117" t="s">
         <v>116</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>115</v>
       </c>
       <c r="H23" s="117" t="s">
         <v>117</v>
       </c>
       <c r="I23" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J23" s="117" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="K23" s="116" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L23" s="116" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M23" s="119" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="N23" s="41"/>
     </row>
-    <row r="24" spans="1:14" ht="13.8" thickBot="1">
+    <row r="24" spans="1:14" ht="13.9" thickBot="1">
       <c r="A24" s="80" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="C24" s="69">
         <v>0.11</v>
@@ -5162,13 +4889,13 @@
         <v>9.4645651104806134</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A25" s="138"/>
       <c r="B25" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C25" s="141">
         <f>SUM(C24:C24)</f>
@@ -5195,7 +4922,7 @@
       <c r="M25" s="143"/>
       <c r="N25" s="25"/>
     </row>
-    <row r="26" spans="1:14" ht="13.8" thickBot="1">
+    <row r="26" spans="1:14" ht="13.9" thickBot="1">
       <c r="B26" s="131"/>
       <c r="C26" s="125"/>
       <c r="D26" s="126"/>
@@ -5212,43 +4939,43 @@
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A27" s="120" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B27" s="252" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C27" s="121" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D27" s="121" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E27" s="121" t="s">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="F27" s="121" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G27" s="121" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="H27" s="121" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="I27" s="121" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J27" s="121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K27" s="121" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L27" s="121" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M27" s="122" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N27" s="14"/>
     </row>
@@ -5257,16 +4984,16 @@
         <v>1</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" s="87" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="F28" s="88">
         <v>48</v>
@@ -5303,16 +5030,16 @@
         <v>10</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D29" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F29" s="95">
         <v>150</v>
@@ -5346,16 +5073,16 @@
         <v>20</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C30" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D30" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F30" s="95">
         <v>70</v>
@@ -5392,16 +5119,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="C31" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E31" s="94" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F31" s="95">
         <v>70</v>
@@ -5438,16 +5165,16 @@
         <v>40</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="C32" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D32" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F32" s="95">
         <v>70</v>
@@ -5484,16 +5211,16 @@
         <v>60</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C33" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D33" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F33" s="95">
         <v>70</v>
@@ -5530,16 +5257,16 @@
         <v>70</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C34" s="93" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D34" s="94" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F34" s="95">
         <v>1.1000000000000001</v>
@@ -5576,13 +5303,13 @@
         <v>80</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="C35" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D35" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E35" s="94"/>
       <c r="F35" s="95">
@@ -5621,10 +5348,10 @@
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D36" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E36" s="94"/>
       <c r="F36" s="95"/>
@@ -5648,18 +5375,18 @@
       </c>
       <c r="N36" s="14"/>
     </row>
-    <row r="37" spans="1:14" ht="13.8" thickBot="1">
+    <row r="37" spans="1:14" ht="13.9" thickBot="1">
       <c r="A37" s="98">
         <v>100</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C37" s="99" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D37" s="100" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E37" s="100"/>
       <c r="F37" s="101"/>
@@ -5689,7 +5416,7 @@
     <row r="38" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="155"/>
       <c r="B38" s="156" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C38" s="156"/>
       <c r="D38" s="156"/>
@@ -5713,7 +5440,7 @@
     <row r="39" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A39" s="153"/>
       <c r="B39" s="139" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C39" s="139"/>
       <c r="D39" s="139"/>
@@ -5731,7 +5458,7 @@
       </c>
       <c r="N39" s="25"/>
     </row>
-    <row r="40" spans="1:14" ht="13.8" thickBot="1">
+    <row r="40" spans="1:14" ht="13.9" thickBot="1">
       <c r="B40" s="144"/>
       <c r="C40" s="125"/>
       <c r="D40" s="126"/>
@@ -5748,41 +5475,41 @@
     </row>
     <row r="41" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A41" s="115" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B41" s="251" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C41" s="117" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D41" s="117" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E41" s="117" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F41" s="117"/>
       <c r="G41" s="117" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="H41" s="117" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="I41" s="117" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="J41" s="117" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="K41" s="117" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L41" s="117" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M41" s="159" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="N41" s="14"/>
     </row>
@@ -5791,16 +5518,16 @@
         <v>50</v>
       </c>
       <c r="B42" s="146" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="C42" s="147" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="D42" s="147" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E42" s="147" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F42" s="147"/>
       <c r="G42" s="148">
@@ -5832,7 +5559,7 @@
     <row r="43" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A43" s="153"/>
       <c r="B43" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C43" s="139"/>
       <c r="D43" s="139"/>
@@ -5853,7 +5580,7 @@
       </c>
       <c r="N43" s="25"/>
     </row>
-    <row r="44" spans="1:14" ht="13.8" thickBot="1">
+    <row r="44" spans="1:14" ht="13.9" thickBot="1">
       <c r="B44" s="144"/>
       <c r="C44" s="125"/>
       <c r="D44" s="126"/>
@@ -5870,26 +5597,26 @@
     </row>
     <row r="45" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A45" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B45" s="250" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C45" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D45" s="116" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="E45" s="116" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="F45" s="116"/>
       <c r="G45" s="116" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="H45" s="119" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="34"/>
@@ -5900,10 +5627,10 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="42" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B46" s="105" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C46" s="259">
         <f>D25</f>
@@ -5925,7 +5652,7 @@
         <v>5.9499999999999997E-2</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J46" s="34"/>
       <c r="K46" s="34"/>
@@ -5935,10 +5662,10 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="257" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B47" s="108" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="C47" s="260">
         <f>D25</f>
@@ -5960,7 +5687,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J47" s="34"/>
       <c r="K47" s="34"/>
@@ -5970,10 +5697,10 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="257" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B48" s="108" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="C48" s="253"/>
       <c r="D48" s="254"/>
@@ -5988,7 +5715,7 @@
         <v>11.994272981514918</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J48" s="34"/>
       <c r="K48" s="34"/>
@@ -5996,12 +5723,12 @@
       <c r="M48" s="34"/>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" ht="13.8" thickBot="1">
+    <row r="49" spans="1:14" ht="13.9" thickBot="1">
       <c r="A49" s="258" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B49" s="111" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="C49" s="255"/>
       <c r="D49" s="256"/>
@@ -6069,151 +5796,151 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4299FED-E1C8-4F90-9407-1DD71F9F06D8}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" style="14" customWidth="1"/>
-    <col min="3" max="5" width="11.6640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="14" customWidth="1"/>
-    <col min="8" max="9" width="10.6640625" style="14" customWidth="1"/>
-    <col min="10" max="11" width="11.33203125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="82.6640625" style="13" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="14"/>
+    <col min="1" max="1" width="5.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" style="14" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="14" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="14" customWidth="1"/>
+    <col min="10" max="11" width="11.28515625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="82.7109375" style="13" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A1" s="270"/>
+    <row r="1" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A1" s="309"/>
       <c r="B1" s="36" t="s">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="12"/>
       <c r="G1" s="37" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="J1" s="48">
         <v>44599</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L1" s="49">
         <v>0</v>
       </c>
       <c r="M1" s="50"/>
       <c r="N1" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20.399999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="270"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20.45" customHeight="1" thickBot="1">
+      <c r="A2" s="309"/>
       <c r="B2" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="274" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="275"/>
-      <c r="E2" s="276"/>
+        <v>74</v>
+      </c>
+      <c r="C2" s="297" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="298"/>
+      <c r="E2" s="299"/>
       <c r="F2" s="38" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="274" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="277"/>
+      <c r="H2" s="297" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="298"/>
+      <c r="J2" s="298"/>
+      <c r="K2" s="298"/>
+      <c r="L2" s="305"/>
       <c r="M2" s="34"/>
       <c r="N2" s="13" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="270"/>
+      <c r="A3" s="309"/>
       <c r="B3" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="278" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="279"/>
-      <c r="E3" s="280"/>
+        <v>78</v>
+      </c>
+      <c r="C3" s="300" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="301"/>
+      <c r="E3" s="302"/>
       <c r="F3" s="39" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G3" s="16"/>
-      <c r="H3" s="281" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="282"/>
-      <c r="J3" s="282"/>
-      <c r="K3" s="282"/>
-      <c r="L3" s="283"/>
+      <c r="H3" s="306" t="s">
+        <v>179</v>
+      </c>
+      <c r="I3" s="307"/>
+      <c r="J3" s="307"/>
+      <c r="K3" s="307"/>
+      <c r="L3" s="308"/>
       <c r="M3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="270"/>
+      <c r="A4" s="309"/>
       <c r="B4" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="278" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="279"/>
-      <c r="E4" s="280"/>
+        <v>82</v>
+      </c>
+      <c r="C4" s="300" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="301"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="39" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="52">
         <v>15</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="L4" s="53">
         <v>15</v>
       </c>
       <c r="M4" s="54"/>
     </row>
-    <row r="5" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A5" s="270"/>
+    <row r="5" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A5" s="309"/>
       <c r="B5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="272">
+        <v>86</v>
+      </c>
+      <c r="C5" s="303">
         <v>45803</v>
       </c>
-      <c r="D5" s="273"/>
+      <c r="D5" s="304"/>
       <c r="E5" s="166" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133">
         <v>45950</v>
       </c>
       <c r="H5" s="166" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="I5" s="134"/>
       <c r="J5" s="135">
@@ -6224,8 +5951,8 @@
       <c r="M5" s="54"/>
       <c r="N5" s="41"/>
     </row>
-    <row r="6" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A6" s="271"/>
+    <row r="6" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A6" s="310"/>
       <c r="B6" s="131"/>
       <c r="C6" s="125"/>
       <c r="D6" s="126"/>
@@ -6242,25 +5969,25 @@
     </row>
     <row r="7" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A7" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C7" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D7" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E7" s="117" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F7" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G7" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="17"/>
@@ -6269,15 +5996,15 @@
       <c r="L7" s="18"/>
       <c r="M7" s="55"/>
       <c r="N7" s="261" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="42" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C8" s="56">
         <v>2</v>
@@ -6302,15 +6029,15 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="13" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C9" s="60">
         <v>2</v>
@@ -6335,15 +6062,15 @@
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="13" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C10" s="60">
         <v>2</v>
@@ -6370,7 +6097,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="60"/>
@@ -6392,9 +6119,9 @@
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
     </row>
-    <row r="12" spans="1:14" ht="13.8" thickBot="1">
+    <row r="12" spans="1:14" ht="13.9" thickBot="1">
       <c r="A12" s="44" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="64"/>
@@ -6419,10 +6146,10 @@
     <row r="13" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="138"/>
       <c r="B13" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C13" s="139" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="D13" s="139"/>
       <c r="E13" s="140">
@@ -6441,7 +6168,7 @@
       <c r="M13" s="24"/>
       <c r="N13" s="25"/>
     </row>
-    <row r="14" spans="1:14" ht="13.8" thickBot="1">
+    <row r="14" spans="1:14" ht="13.9" thickBot="1">
       <c r="B14" s="131"/>
       <c r="C14" s="125"/>
       <c r="D14" s="126"/>
@@ -6458,33 +6185,33 @@
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A15" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B15" s="251" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D15" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E15" s="117" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F15" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G15" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C16" s="68">
         <v>2</v>
@@ -6506,10 +6233,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C17" s="73">
         <v>2</v>
@@ -6531,10 +6258,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C18" s="73">
         <v>2</v>
@@ -6556,10 +6283,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C19" s="73">
         <v>2</v>
@@ -6579,9 +6306,9 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.8" thickBot="1">
+    <row r="20" spans="1:14" ht="13.9" thickBot="1">
       <c r="A20" s="45" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="77"/>
@@ -6601,7 +6328,7 @@
     <row r="21" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="138"/>
       <c r="B21" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21" s="139"/>
       <c r="D21" s="139"/>
@@ -6622,7 +6349,7 @@
       <c r="M21" s="24"/>
       <c r="N21" s="25"/>
     </row>
-    <row r="22" spans="1:14" ht="13.8" thickBot="1">
+    <row r="22" spans="1:14" ht="13.9" thickBot="1">
       <c r="B22" s="131"/>
       <c r="C22" s="125"/>
       <c r="D22" s="126"/>
@@ -6639,52 +6366,52 @@
     </row>
     <row r="23" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A23" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B23" s="251" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="C23" s="117" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D23" s="117" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E23" s="117" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="117" t="s">
         <v>116</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>115</v>
       </c>
       <c r="H23" s="117" t="s">
         <v>117</v>
       </c>
       <c r="I23" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J23" s="117" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="K23" s="116" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L23" s="116" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M23" s="119" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="N23" s="41"/>
     </row>
-    <row r="24" spans="1:14" ht="13.8" thickBot="1">
+    <row r="24" spans="1:14" ht="13.9" thickBot="1">
       <c r="A24" s="80" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="C24" s="69">
         <v>0.22</v>
@@ -6726,13 +6453,13 @@
         <v>9.4645651104806134</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A25" s="138"/>
       <c r="B25" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C25" s="141">
         <f>SUM(C24:C24)</f>
@@ -6759,7 +6486,7 @@
       <c r="M25" s="143"/>
       <c r="N25" s="25"/>
     </row>
-    <row r="26" spans="1:14" ht="13.8" thickBot="1">
+    <row r="26" spans="1:14" ht="13.9" thickBot="1">
       <c r="B26" s="131"/>
       <c r="C26" s="125"/>
       <c r="D26" s="126"/>
@@ -6776,43 +6503,43 @@
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A27" s="120" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B27" s="252" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C27" s="121" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D27" s="121" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E27" s="121" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F27" s="121" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G27" s="121" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="H27" s="121" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="I27" s="121" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J27" s="121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K27" s="121" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L27" s="121" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M27" s="122" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N27" s="14"/>
     </row>
@@ -6821,16 +6548,16 @@
         <v>1</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" s="87" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="F28" s="88">
         <v>48</v>
@@ -6867,16 +6594,16 @@
         <v>10</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D29" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F29" s="95">
         <v>150</v>
@@ -6913,16 +6640,16 @@
         <v>20</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C30" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D30" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F30" s="95">
         <v>70</v>
@@ -6959,16 +6686,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="C31" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E31" s="94" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F31" s="95">
         <v>70</v>
@@ -7005,16 +6732,16 @@
         <v>40</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="C32" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D32" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F32" s="95">
         <v>70</v>
@@ -7051,16 +6778,16 @@
         <v>60</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C33" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D33" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F33" s="95">
         <v>70</v>
@@ -7097,16 +6824,16 @@
         <v>70</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C34" s="93" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D34" s="94" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F34" s="95">
         <v>1.1000000000000001</v>
@@ -7143,13 +6870,13 @@
         <v>80</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="C35" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D35" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E35" s="94"/>
       <c r="F35" s="95">
@@ -7188,10 +6915,10 @@
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D36" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E36" s="94"/>
       <c r="F36" s="95"/>
@@ -7212,18 +6939,18 @@
       </c>
       <c r="N36" s="14"/>
     </row>
-    <row r="37" spans="1:14" ht="13.8" thickBot="1">
+    <row r="37" spans="1:14" ht="13.9" thickBot="1">
       <c r="A37" s="98">
         <v>100</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C37" s="99" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D37" s="100" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E37" s="100"/>
       <c r="F37" s="101"/>
@@ -7253,7 +6980,7 @@
     <row r="38" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="155"/>
       <c r="B38" s="156" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C38" s="156"/>
       <c r="D38" s="156"/>
@@ -7277,7 +7004,7 @@
     <row r="39" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A39" s="153"/>
       <c r="B39" s="139" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C39" s="139"/>
       <c r="D39" s="139"/>
@@ -7295,7 +7022,7 @@
       </c>
       <c r="N39" s="25"/>
     </row>
-    <row r="40" spans="1:14" ht="13.8" thickBot="1">
+    <row r="40" spans="1:14" ht="13.9" thickBot="1">
       <c r="B40" s="144"/>
       <c r="C40" s="125"/>
       <c r="D40" s="126"/>
@@ -7312,41 +7039,41 @@
     </row>
     <row r="41" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A41" s="115" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B41" s="251" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C41" s="117" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D41" s="117" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E41" s="117" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F41" s="117"/>
       <c r="G41" s="117" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="H41" s="117" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="I41" s="117" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="J41" s="117" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="K41" s="117" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L41" s="117" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M41" s="159" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="N41" s="14"/>
     </row>
@@ -7355,16 +7082,16 @@
         <v>50</v>
       </c>
       <c r="B42" s="146" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="C42" s="147" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="D42" s="147" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E42" s="147" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F42" s="147"/>
       <c r="G42" s="148">
@@ -7396,7 +7123,7 @@
     <row r="43" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A43" s="153"/>
       <c r="B43" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C43" s="139"/>
       <c r="D43" s="139"/>
@@ -7417,7 +7144,7 @@
       </c>
       <c r="N43" s="25"/>
     </row>
-    <row r="44" spans="1:14" ht="13.8" thickBot="1">
+    <row r="44" spans="1:14" ht="13.9" thickBot="1">
       <c r="B44" s="144"/>
       <c r="C44" s="125"/>
       <c r="D44" s="126"/>
@@ -7434,26 +7161,26 @@
     </row>
     <row r="45" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A45" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B45" s="250" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="C45" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D45" s="116" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="E45" s="116" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="F45" s="116"/>
       <c r="G45" s="116" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="H45" s="119" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="34"/>
@@ -7464,10 +7191,10 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="42" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B46" s="105" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C46" s="259">
         <f>D25</f>
@@ -7489,7 +7216,7 @@
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J46" s="34"/>
       <c r="K46" s="34"/>
@@ -7499,10 +7226,10 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="257" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B47" s="108" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="C47" s="260">
         <f>D25</f>
@@ -7524,7 +7251,7 @@
         <v>0.05</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J47" s="34"/>
       <c r="K47" s="34"/>
@@ -7534,10 +7261,10 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="257" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B48" s="108" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="C48" s="253"/>
       <c r="D48" s="254"/>
@@ -7552,7 +7279,7 @@
         <v>23.582184257243572</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J48" s="34"/>
       <c r="K48" s="34"/>
@@ -7560,12 +7287,12 @@
       <c r="M48" s="34"/>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" ht="13.8" thickBot="1">
+    <row r="49" spans="1:14" ht="13.9" thickBot="1">
       <c r="A49" s="258" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B49" s="111" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="C49" s="255"/>
       <c r="D49" s="256"/>
@@ -7630,151 +7357,151 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB323336-6B5E-4CB8-AB86-BADFF21EBA5B}">
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" style="14" customWidth="1"/>
-    <col min="3" max="5" width="11.6640625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="14" customWidth="1"/>
-    <col min="8" max="9" width="10.6640625" style="14" customWidth="1"/>
-    <col min="10" max="11" width="11.33203125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="82.6640625" style="13" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="14"/>
+    <col min="1" max="1" width="5.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" style="14" customWidth="1"/>
+    <col min="3" max="5" width="11.7109375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="14" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="14" customWidth="1"/>
+    <col min="10" max="11" width="11.28515625" style="14" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="82.7109375" style="13" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A1" s="270"/>
+    <row r="1" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A1" s="309"/>
       <c r="B1" s="36" t="s">
-        <v>187</v>
+        <v>68</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
       <c r="F1" s="12"/>
       <c r="G1" s="37" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="H1" s="47" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="J1" s="48">
         <v>44599</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="L1" s="49">
         <v>0</v>
       </c>
       <c r="M1" s="50"/>
       <c r="N1" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20.399999999999999" customHeight="1" thickBot="1">
-      <c r="A2" s="270"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20.45" customHeight="1" thickBot="1">
+      <c r="A2" s="309"/>
       <c r="B2" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="274" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="275"/>
-      <c r="E2" s="276"/>
+        <v>74</v>
+      </c>
+      <c r="C2" s="297" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="298"/>
+      <c r="E2" s="299"/>
       <c r="F2" s="38" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="274" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="277"/>
+      <c r="H2" s="297" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="298"/>
+      <c r="J2" s="298"/>
+      <c r="K2" s="298"/>
+      <c r="L2" s="305"/>
       <c r="M2" s="34"/>
       <c r="N2" s="13" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" thickBot="1">
-      <c r="A3" s="270"/>
+      <c r="A3" s="309"/>
       <c r="B3" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="278" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="279"/>
-      <c r="E3" s="280"/>
+        <v>78</v>
+      </c>
+      <c r="C3" s="300" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="301"/>
+      <c r="E3" s="302"/>
       <c r="F3" s="39" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G3" s="16"/>
-      <c r="H3" s="281" t="s">
-        <v>180</v>
-      </c>
-      <c r="I3" s="282"/>
-      <c r="J3" s="282"/>
-      <c r="K3" s="282"/>
-      <c r="L3" s="283"/>
+      <c r="H3" s="306" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="307"/>
+      <c r="J3" s="307"/>
+      <c r="K3" s="307"/>
+      <c r="L3" s="308"/>
       <c r="M3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="270"/>
+      <c r="A4" s="309"/>
       <c r="B4" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="278" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="279"/>
-      <c r="E4" s="280"/>
+        <v>82</v>
+      </c>
+      <c r="C4" s="300" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="301"/>
+      <c r="E4" s="302"/>
       <c r="F4" s="39" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G4" s="51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="52">
         <v>16</v>
       </c>
       <c r="K4" s="40" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="L4" s="53">
         <v>16</v>
       </c>
       <c r="M4" s="54"/>
     </row>
-    <row r="5" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A5" s="270"/>
+    <row r="5" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A5" s="309"/>
       <c r="B5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="272">
+        <v>86</v>
+      </c>
+      <c r="C5" s="303">
         <v>45803</v>
       </c>
-      <c r="D5" s="273"/>
+      <c r="D5" s="304"/>
       <c r="E5" s="166" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133">
         <v>45950</v>
       </c>
       <c r="H5" s="166" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="I5" s="134"/>
       <c r="J5" s="135">
@@ -7785,8 +7512,8 @@
       <c r="M5" s="54"/>
       <c r="N5" s="41"/>
     </row>
-    <row r="6" spans="1:14" ht="13.8" thickBot="1">
-      <c r="A6" s="271"/>
+    <row r="6" spans="1:14" ht="13.9" thickBot="1">
+      <c r="A6" s="310"/>
       <c r="B6" s="131"/>
       <c r="C6" s="125"/>
       <c r="D6" s="126"/>
@@ -7803,25 +7530,25 @@
     </row>
     <row r="7" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A7" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B7" s="250" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C7" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D7" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E7" s="117" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F7" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G7" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="17"/>
@@ -7830,15 +7557,15 @@
       <c r="L7" s="18"/>
       <c r="M7" s="55"/>
       <c r="N7" s="261" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="42" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C8" s="56">
         <v>3</v>
@@ -7863,15 +7590,15 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="13" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C9" s="60">
         <v>3</v>
@@ -7896,15 +7623,15 @@
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="13" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C10" s="60">
         <v>3</v>
@@ -7931,7 +7658,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="43" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="60"/>
@@ -7953,9 +7680,9 @@
       <c r="L11" s="18"/>
       <c r="M11" s="18"/>
     </row>
-    <row r="12" spans="1:14" ht="13.8" thickBot="1">
+    <row r="12" spans="1:14" ht="13.9" thickBot="1">
       <c r="A12" s="44" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="64"/>
@@ -7980,10 +7707,10 @@
     <row r="13" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="138"/>
       <c r="B13" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C13" s="139" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="D13" s="139"/>
       <c r="E13" s="140">
@@ -8002,7 +7729,7 @@
       <c r="M13" s="24"/>
       <c r="N13" s="25"/>
     </row>
-    <row r="14" spans="1:14" ht="13.8" thickBot="1">
+    <row r="14" spans="1:14" ht="13.9" thickBot="1">
       <c r="B14" s="131"/>
       <c r="C14" s="125"/>
       <c r="D14" s="126"/>
@@ -8019,33 +7746,33 @@
     </row>
     <row r="15" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A15" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B15" s="251" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D15" s="117" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E15" s="117" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F15" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="G15" s="118" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C16" s="68">
         <v>3</v>
@@ -8067,10 +7794,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C17" s="73">
         <v>3</v>
@@ -8092,10 +7819,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C18" s="73">
         <v>3</v>
@@ -8117,10 +7844,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="43" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="C19" s="73">
         <v>3</v>
@@ -8140,9 +7867,9 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.8" thickBot="1">
+    <row r="20" spans="1:14" ht="13.9" thickBot="1">
       <c r="A20" s="45" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="77"/>
@@ -8162,7 +7889,7 @@
     <row r="21" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A21" s="138"/>
       <c r="B21" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C21" s="139"/>
       <c r="D21" s="139"/>
@@ -8183,7 +7910,7 @@
       <c r="M21" s="24"/>
       <c r="N21" s="25"/>
     </row>
-    <row r="22" spans="1:14" ht="13.8" thickBot="1">
+    <row r="22" spans="1:14" ht="13.9" thickBot="1">
       <c r="B22" s="131"/>
       <c r="C22" s="125"/>
       <c r="D22" s="126"/>
@@ -8200,52 +7927,52 @@
     </row>
     <row r="23" spans="1:14" s="19" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A23" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B23" s="251" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="C23" s="117" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D23" s="117" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E23" s="117" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="117" t="s">
         <v>116</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>115</v>
       </c>
       <c r="H23" s="117" t="s">
         <v>117</v>
       </c>
       <c r="I23" s="117" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="J23" s="117" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="K23" s="116" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L23" s="116" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M23" s="119" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="N23" s="41"/>
     </row>
-    <row r="24" spans="1:14" ht="13.8" thickBot="1">
+    <row r="24" spans="1:14" ht="13.9" thickBot="1">
       <c r="A24" s="80" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C24" s="69">
         <v>2</v>
@@ -8287,13 +8014,13 @@
         <v>2.2300748001031723</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A25" s="138"/>
       <c r="B25" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C25" s="141">
         <f>SUM(C24:C24)</f>
@@ -8320,7 +8047,7 @@
       <c r="M25" s="143"/>
       <c r="N25" s="25"/>
     </row>
-    <row r="26" spans="1:14" ht="13.8" thickBot="1">
+    <row r="26" spans="1:14" ht="13.9" thickBot="1">
       <c r="B26" s="131"/>
       <c r="C26" s="125"/>
       <c r="D26" s="126"/>
@@ -8337,43 +8064,43 @@
     </row>
     <row r="27" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A27" s="120" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B27" s="252" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="C27" s="121" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D27" s="121" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E27" s="121" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F27" s="121" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G27" s="121" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="H27" s="121" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="I27" s="121" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J27" s="121" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K27" s="121" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="L27" s="121" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M27" s="122" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N27" s="14"/>
     </row>
@@ -8382,16 +8109,16 @@
         <v>1</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" s="87" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E28" s="87" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="F28" s="88">
         <v>48</v>
@@ -8428,16 +8155,16 @@
         <v>10</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D29" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F29" s="95">
         <v>150</v>
@@ -8474,16 +8201,16 @@
         <v>20</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C30" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D30" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F30" s="95">
         <v>70</v>
@@ -8520,16 +8247,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="C31" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E31" s="94" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F31" s="95">
         <v>70</v>
@@ -8566,16 +8293,16 @@
         <v>40</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="C32" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D32" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E32" s="94" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F32" s="95">
         <v>70</v>
@@ -8612,16 +8339,16 @@
         <v>60</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C33" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D33" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E33" s="94" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F33" s="95">
         <v>70</v>
@@ -8658,16 +8385,16 @@
         <v>70</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C34" s="93" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D34" s="94" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E34" s="94" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F34" s="95">
         <v>1.1000000000000001</v>
@@ -8704,13 +8431,13 @@
         <v>80</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="C35" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D35" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E35" s="94"/>
       <c r="F35" s="95">
@@ -8749,10 +8476,10 @@
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="93" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D36" s="94" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E36" s="94"/>
       <c r="F36" s="95"/>
@@ -8773,18 +8500,18 @@
       </c>
       <c r="N36" s="14"/>
     </row>
-    <row r="37" spans="1:14" ht="13.8" thickBot="1">
+    <row r="37" spans="1:14" ht="13.9" thickBot="1">
       <c r="A37" s="98">
         <v>100</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C37" s="99" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D37" s="100" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="E37" s="100"/>
       <c r="F37" s="101"/>
@@ -8814,7 +8541,7 @@
     <row r="38" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="155"/>
       <c r="B38" s="156" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="C38" s="156"/>
       <c r="D38" s="156"/>
@@ -8838,7 +8565,7 @@
     <row r="39" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A39" s="153"/>
       <c r="B39" s="139" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C39" s="139"/>
       <c r="D39" s="139"/>
@@ -8856,7 +8583,7 @@
       </c>
       <c r="N39" s="25"/>
     </row>
-    <row r="40" spans="1:14" ht="13.8" thickBot="1">
+    <row r="40" spans="1:14" ht="13.9" thickBot="1">
       <c r="B40" s="144"/>
       <c r="C40" s="125"/>
       <c r="D40" s="126"/>
@@ -8873,41 +8600,41 @@
     </row>
     <row r="41" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A41" s="115" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B41" s="251" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C41" s="117" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D41" s="117" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E41" s="117" t="s">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F41" s="117"/>
       <c r="G41" s="117" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="H41" s="117" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="I41" s="117" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="J41" s="117" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="K41" s="117" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="L41" s="117" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M41" s="159" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="N41" s="14"/>
     </row>
@@ -8916,16 +8643,16 @@
         <v>50</v>
       </c>
       <c r="B42" s="146" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="C42" s="147" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="D42" s="147" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E42" s="147" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F42" s="147"/>
       <c r="G42" s="148">
@@ -8957,7 +8684,7 @@
     <row r="43" spans="1:14" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A43" s="153"/>
       <c r="B43" s="139" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C43" s="139"/>
       <c r="D43" s="139"/>
@@ -8978,7 +8705,7 @@
       </c>
       <c r="N43" s="25"/>
     </row>
-    <row r="44" spans="1:14" ht="13.8" thickBot="1">
+    <row r="44" spans="1:14" ht="13.9" thickBot="1">
       <c r="B44" s="144"/>
       <c r="C44" s="125"/>
       <c r="D44" s="126"/>
@@ -8995,26 +8722,26 @@
     </row>
     <row r="45" spans="1:14" ht="27" customHeight="1" thickBot="1">
       <c r="A45" s="115" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="B45" s="250" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="C45" s="116" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D45" s="116" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="E45" s="116" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="F45" s="116"/>
       <c r="G45" s="116" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="H45" s="119" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="I45" s="34"/>
       <c r="J45" s="34"/>
@@ -9025,10 +8752,10 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="42" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B46" s="105" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C46" s="259">
         <f>D25</f>
@@ -9050,7 +8777,7 @@
         <v>0.7</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J46" s="34"/>
       <c r="K46" s="34"/>
@@ -9060,10 +8787,10 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="257" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="B47" s="108" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="C47" s="260">
         <f>D25</f>
@@ -9085,7 +8812,7 @@
         <v>0.5</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J47" s="34"/>
       <c r="K47" s="34"/>
@@ -9095,10 +8822,10 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="257" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B48" s="108" t="s">
-        <v>5</v>
+        <v>176</v>
       </c>
       <c r="C48" s="253"/>
       <c r="D48" s="254"/>
@@ -9113,7 +8840,7 @@
         <v>43.759097240134125</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="J48" s="34"/>
       <c r="K48" s="34"/>
@@ -9121,12 +8848,12 @@
       <c r="M48" s="34"/>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" ht="13.8" thickBot="1">
+    <row r="49" spans="1:14" ht="13.9" thickBot="1">
       <c r="A49" s="258" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B49" s="111" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="C49" s="255"/>
       <c r="D49" s="256"/>
